--- a/data/availability/projects/ilcazar/creek-town.xlsx
+++ b/data/availability/projects/ilcazar/creek-town.xlsx
@@ -461,12 +461,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Creek Town latest availability</t>
+          <t>Updated inventory for creek-town</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,17 +582,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Creek Town</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10% over 8 years · Maintenance 10%</t>
+          <t>10% over 8 years; Maintenance: 10%</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Creek Town</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10% over 8 years · Maintenance 10%</t>
+          <t>10% over 8 years; Maintenance: 10%</t>
         </is>
       </c>
     </row>
@@ -682,17 +682,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Creek Town</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10% over 8 years · Maintenance 10%</t>
+          <t>10% over 8 years; Maintenance: 10%</t>
         </is>
       </c>
     </row>
@@ -704,26 +704,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>185</v>
       </c>
       <c r="F5" t="n">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="G5" t="n">
         <v>25.45</v>
       </c>
       <c r="H5" t="n">
-        <v>28.71</v>
+        <v>25.45</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -732,12 +732,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Town Villas</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -754,43 +754,93 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Standalone Villa</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
+        <v>210</v>
+      </c>
+      <c r="F6" t="n">
+        <v>210</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="H6" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Core &amp; Shell</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ready To Move</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% over 10 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>creek-town</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>420</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>420</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>75</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" t="n">
         <v>75</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Core &amp; Shell</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Prime Villas</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Ready to Move (RTM)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>New Cairo</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ready To Move</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>15% over 5 years</t>
         </is>
@@ -890,12 +940,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CT-2BD-128</t>
+          <t>CT-2BD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Creek Town</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -909,10 +959,14 @@
       <c r="G2" t="n">
         <v>128</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>128 SQM</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -920,12 +974,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10% over 8 years · Maintenance 10%</t>
+          <t>10% over 8 years; Maintenance: 10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -947,12 +1001,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CT-3BD-165</t>
+          <t>CT-3BD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Creek Town</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -966,10 +1020,14 @@
       <c r="G3" t="n">
         <v>165</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>165 SQM</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -977,12 +1035,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10% over 8 years · Maintenance 10%</t>
+          <t>10% over 8 years; Maintenance: 10%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1004,12 +1062,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CT-PENT-190</t>
+          <t>CT-PH</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Creek Town</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1023,10 +1081,14 @@
       <c r="G4" t="n">
         <v>190</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>190 SQM Penthouse</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1034,12 +1096,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10% over 8 years · Maintenance 10%</t>
+          <t>10% over 8 years; Maintenance: 10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1056,7 +1118,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1066,7 +1128,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Town Villas</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1080,18 +1142,22 @@
       <c r="G5" t="n">
         <v>185</v>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>185 SQM Town Villa</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>25445545</v>
+        <v>25445544</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1113,7 +1179,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1123,11 +1189,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Town Villas</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1137,10 +1203,14 @@
       <c r="G6" t="n">
         <v>210</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>210 SQM Town Villa</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1148,7 +1218,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1175,12 +1245,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CT-PV-420</t>
+          <t>CT-PV-SA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prime Villas</t>
+          <t>New Cairo</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1194,10 +1264,14 @@
       <c r="G7" t="n">
         <v>420</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>420 SQM Prime Villa Standalone</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Landscape / View</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1205,7 +1279,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Ready to Move (RTM)</t>
+          <t>Ready To Move</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">

--- a/data/availability/projects/ilcazar/creek-town.xlsx
+++ b/data/availability/projects/ilcazar/creek-town.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Updated inventory for creek-town</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
